--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>이슈메모</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1785207578455</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
+        <v>120</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,46 @@
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1785208657443</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H3" t="n">
+        <v>120</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,46 @@
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1785208660199</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1785208657443</v>
+        <v>1785208660199</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -559,46 +559,6 @@
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1785208660199</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>03:17</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>70</v>
-      </c>
-      <c r="H4" t="n">
-        <v>120</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,46 +519,6 @@
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1785208660199</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>03:17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H3" t="n">
-        <v>120</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,50 @@
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1787004604500</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Element 하부 접착 고무 두께 10mm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,50 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1787004612279</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Element 하부 접착 고무 두께 10mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1787004604500</v>
+        <v>1787004612279</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -556,53 +556,9 @@
         <v>18</v>
       </c>
       <c r="I3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>Element 하부 접착 고무 두께 10mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1787004612279</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>22:10</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>Element 하부 접착 고무 두께 10mm</t>
         </is>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,46 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1787884350026</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>120</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,16 +522,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1787004612279</v>
+        <v>1787884350026</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>02:32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AR-F5103A</t>
+          <t>AR-F5203</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -550,59 +550,15 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Element 하부 접착 고무 두께 10mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1787884350026</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>02:32</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>신우</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>120</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/filter_usage_HOU.xlsx
+++ b/filter_usage_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,50 @@
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1787884613158</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Element 하부 접착 고무 두께 10mm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
